--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_014/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_014/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -394,6 +399,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -550,46 +560,6 @@
       </text>
     </comment>
     <comment ref="I7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="A8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="H8" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="I8" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1346,12 +1316,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Predict peak stress and deflection in Al 7075-T7351 avionics corner bracket under worst-case ascent quasi-static and sine-sweep loads</t>
+          <t>Predict peak stress and deflection in Al 7075-T7351 avionics bay corner bracket under worst-case quasi-static and sine-sweep loads for PDR clearance</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Static structural FEA of the LTV-2 avionics bay corner bracket (P/N LTV2-AVB-003) using Ansys Mechanical 2024 R1. The model supports a PDR decision to clear the bracket geometry against yield safety factor, connector-face deflection, and joint-clamp-loss acceptance targets under combined in-plane shear and out-of-plane bending from avionics mass and harness loads. Acoustic random/PSD, thermal gradients, fatigue, and manufacturing tolerance effects are explicitly deferred to CDR.</t>
+          <t>Static structural FEA of P/N LTV2-AVB-003 avionics bracket using Ansys Mechanical 2024 R1 to establish yield safety factors and connector-face deflection margins for the Lunar Terrain Vehicle ascent-stage combined in-plane shear and out-of-plane bending load case. Outputs are compared against PDR acceptance targets: yield FoS ≥ 1.25, deflection ≤ 0.40 mm, and no net interface separation.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1381,7 +1351,7 @@
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>M. Chen (Structures); peer check: M. Alvarez</t>
+          <t>M. Chen (Structures); peer check M. Alvarez</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1389,9 +1359,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1510,7 +1480,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>PDR Acceptance Targets — Yield Margin, Deflection, and Joint Integrity</t>
+          <t>PDR Structural Acceptance Targets — LTV2-AVB-003</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1520,7 +1490,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Yield safety factor ≥ 1.25 on primary load case; connector-face deflection ≤ 0.40 mm under sine-peak equivalent load; no net interface separation (positive contact pressure) under worst preload scatter</t>
+          <t>Yield safety factor ≥ 1.25 on primary load case; connector-face deflection ≤ 0.40 mm under sine-peak equivalent load; no net separation at interface under worst preload scatter</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1542,12 +1512,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Ansys Mechanical 2024 R1 Static FEA — AVB_24R1_PDR</t>
+          <t>Ansys Mechanical FEA Model — AVB_24R1_PDR</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Quadratic tet (SOLID186) model with frictional contact, bolt pretension elements, and bilinear kinematic hardening for Al 7075-T7351; fine mesh ~3.6M DOF; input deck CRC32 D3A4-9F11</t>
+          <t>Quasi-static structural model of Al 7075-T7351 corner bracket using SOLID186 quadratic tets with frictional contact (augmented Lagrange) and bolt pretension elements; Ansys Mechanical 2024 R1 build 24.1.108</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1529,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Material Properties — Al 7075-T7351 Heat 7A-26</t>
+          <t>Material Data — Al 7075-T7351 Heat 7A-26</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Mill cert plus 3 tensile coupons from sister plate (E=72.1±0.8 GPa, Fy=442±6 MPa); supplemented by MMPDS-17 Table 3.7.2.0(b) allowables</t>
+          <t>MMPDS-17 tabulated properties plus mill certificate and 3-coupon tensile tests from sister plate; E = 72.1 ± 0.8 GPa, Fy = 442 ± 6 MPa</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1546,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Subcomponent Static Pull Test — Single Bracket</t>
+          <t>Subcomponent Static Pull Test Data</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Load-deflection (LVDT) and strain-gauge (G1–G4) data from single bracket on 12 mm 7075 base plate; ultrasonic bolt-load measurements 9.1–10.0 kN; DIC-based yield onset at 27.0–27.5 kN</t>
+          <t>Strain gauge (G1–G4), LVDT, DIC, and ultrasonic bolt-load measurements from single-bracket pull test used for model validation comparison</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2018,7 +1988,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>NAFEMS LE10 Plate-with-Hole Benchmark</t>
+          <t>Mesh Convergence Study</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2033,27 +2003,27 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Quarter-symmetry SOLID186 model of NAFEMS LE10 tension case; stress concentration compared to analytical Kt=3.00</t>
+          <t>Three-mesh refinement study (coarse ~0.9M DOF, medium ~1.8M DOF, fine ~3.6M DOF) assessing tip deflection and peak von Mises stress convergence at hotspot locations</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Analytical stress concentration factor Kt = 3.00</t>
+          <t>Richardson/linear extrapolation of hotspot stress; change between medium and fine meshes</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>If Yes, describe the method</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Linear extrapolation (quarter-point method); percentage change between mesh levels</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Model Kt = 2.98 (0.7% low)</t>
+          <t>Deflection change med→fine = 1.2%; stress change med→fine = 2.1%; extrapolated hotspot stress 328 ± 8 MPa</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2065,7 +2035,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Cantilever Beam Tip Deflection Benchmark</t>
+          <t>Solver Convergence and Numerical Health Checks</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2075,12 +2045,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>200×25×5 mm beam, E=70 GPa, 500 N tip load; model deflection compared to closed-form Euler-Bernoulli solution</t>
+          <t>Iterative solver residual monitoring, contact penetration, energy balance, and reproducibility check across two independent contact initializations</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Analytical tip deflection δ = 9.14 mm</t>
+          <t>Residual targets of 0.1% for force and displacement; energy balance criterion</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2090,7 +2060,7 @@
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>Model δ = 9.11 mm (0.3% low)</t>
+          <t>Max contact penetration 5.8 µm; energy balance error 0.4%; deflection reproducibility within 0.2%</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2102,7 +2072,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Hertz Contact Sanity Test</t>
+          <t>Code Verification — NAFEMS LE10 and Analytical Benchmarks</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2112,12 +2082,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Cylinder-on-flat compression compared to Hertz contact solution; refined contact-patch mesh assessed</t>
+          <t>Reproduced NAFEMS LE10 plate-with-hole Kt benchmark, cantilever tip deflection (closed-form), and Hertz contact cylinder-on-flat to verify element formulation and contact settings</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Hertz analytical contact solution</t>
+          <t>Analytical solutions and NAFEMS reference value Kt = 3.00; Hertz contact theory</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2127,7 +2097,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>Coarse mesh 8% error; refined mesh (0.3 mm elements) 2.5% error</t>
+          <t>LE10 Kt = 2.98 (0.7% low); cantilever 0.3% low; refined Hertz error 2.5%</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2139,7 +2109,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Mesh Refinement / Discretization Convergence Study</t>
+          <t>Subcomponent Static Pull Test — Model vs Experiment Comparison</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2149,12 +2119,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Three-mesh study (coarse ~0.9M, medium ~1.8M, fine ~3.6M DOF) on connector-face deflection and peak von Mises stress at inner fillet; Richardson/linear extrapolation applied at hotspot</t>
+          <t>Comparison of load–deflection slope, peak fillet strain (gauge G1), and plasticity onset load between FEA predictions and physical bracket test with strain gauges, LVDT, and DIC</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Convergence to mesh-independent value; linear extrapolation gives 328±8 MPa at hotspot</t>
+          <t>Single-bracket static pull test with calibrated instrumentation</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2164,12 +2134,12 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Linear (quarter-point) hotspot extrapolation; change-metric between mesh levels</t>
+          <t>Measured preload scatter (9.1–10.0 kN ultrasonic), friction range (µ 0.23–0.28) characterised and compared to model nominal inputs</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Medium-to-fine change: deflection 1.2%, stress 2.1%; extrapolated hotspot 328±8 MPa</t>
+          <t>Deflection slope: model +3.9% vs test; peak strain G1: model +4.2% vs test; plasticity onset: model 27.5 kN vs test 27.0–27.5 kN</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2181,7 +2151,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Subcomponent Static Pull Test — Model vs Experiment</t>
+          <t>Parametric Uncertainty Quantification — Latin Hypercube Sweep</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2191,12 +2161,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Comparison of load-deflection stiffness, peak fillet strain, and yield-onset load between FEA and physical bracket pull test</t>
+          <t>250-sample Latin hypercube propagation of four uncertain inputs (E, µ, bolt preload, fillet radius) to deflection and hotspot stress; 95th-percentile margins checked against acceptance targets</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Experimental LVDT stiffness 7.24 kN/mm, strain gauge G1 peak 3,120 µε, DIC yield onset 27.0–27.5 kN</t>
+          <t>PDR acceptance targets: FoS_y ≥ 1.25, deflection ≤ 0.40 mm</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2206,57 +2176,15 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Measured bolt preload scatter (9.1–10.0 kN) and friction range (0.23–0.28) compared to model nominals; parametric sensitivity sweeps</t>
+          <t>Latin hypercube sampling (250 samples); normal and uniform input distributions; 95th-percentile output statistics</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>Stiffness error +3.9%; strain error +4.2%; yield onset match within 0–1.9%</t>
+          <t>Deflection 95th pct = 0.329 mm &lt; 0.40 mm limit; FoS_y(95%) = 1.29 &gt; 1.25 requirement; hotspot stress 95th pct = 336 MPa</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Latin Hypercube UQ Sweep — Margin Assessment</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>ValidationResult</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>250-sample LHC propagation of E, µ, bolt preload, and fillet radius uncertainties; 95th-percentile outcomes compared to acceptance targets</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>PDR acceptance targets: FoS_y ≥ 1.25; deflection ≤ 0.40 mm</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>Latin Hypercube Sampling (250 samples), normal and uniform input distributions</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>95th-pct deflection 0.329 mm &lt; 0.40 mm; 95th-pct stress 336 MPa → FoS_y(95%) = 1.29 ≥ 1.25</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2407,12 +2335,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented version, archived solver logs, and CRC-verified input deck</t>
+          <t>Commercial solver with traceable version, archived inputs, and checksum-verified solution files</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Ansys Mechanical 2024 R1 Solver Build 24.1.108 is a commercial solver with implicit quality assurance processes. Workbench project archived in Git LFS at tag v0.9-PDR; solver logs archived with checksum; input deck CRC32 D3A4-9F11 documented. Version is fully traceable. No explicit Ansys quality-cert document is cited in the report, and no independent regression test suite evidence is provided beyond standard commercial practice.</t>
+          <t>Ansys Mechanical 2024 R1 (build 24.1.108) is a commercially maintained solver. Workbench project stored in Git LFS with tag v0.9-PDR; solver logs archived with CRC32 checksum D3A4-9F11; solution controls exported as XML. No explicit ISO quality certification or regression-test report is cited, but version control, checksums, and archival are documented in Slide 12. Commercial solver pedigree provides baseline SQA assurance.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2441,12 +2369,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Reproduction of analytical or accepted benchmark solutions within acceptable tolerance</t>
+          <t>Code reproduces analytical or standard benchmark solutions within a few percent for the relevant element type and contact formulation</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Three code-level benchmarks performed: (1) NAFEMS LE10 plate-with-hole — model Kt 2.98 vs analytical 3.00 (0.7%); (2) cantilever beam tip deflection — model 9.11 mm vs analytical 9.14 mm (0.3%); (3) Hertz cylinder-on-flat contact — refined mesh error 2.5%. These benchmarks validate SOLID186 element formulation and augmented-Lagrange contact settings. Coverage is solid for linear and contact physics but no MMS or published benchmark suite is cited.</t>
+          <t>Slide 8 documents three independent benchmarks: NAFEMS LE10 plate-with-hole (Kt error 0.7%), cantilever tip deflection closed-form (0.3%), and Hertz cylinder-on-flat contact (2.5% after mesh refinement). These cover the two primary physics modes (continuum stress and frictional contact) used in the bracket model. Results are within acceptable engineering tolerances for a PDR-stage analysis.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2475,12 +2403,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with quantified remaining error on primary QoIs</t>
+          <t>Mesh convergence demonstrated with quantified change between refinement levels; remaining discretization impact documented</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement study (coarse 0.9M, medium 1.8M, fine 3.6M DOF). Medium-to-fine change: connector deflection 1.2%, peak von Mises stress 2.1%. Linear (quarter-point) hotspot extrapolation gives 328±8 MPa at inner fillet. Remaining discretization impact documented as &lt;1.5% on deflection and &lt;3% on stress. Element quality metrics (Jacobian &gt;0.55, skewness &lt;0.75, minimum 4 elements through web) also reported. Quantified uncertainty bound on extrapolated stress provided. GCI/Richardson extrapolation not applied formally but trend is clearly convergent.</t>
+          <t>Slide 5 presents a three-level mesh refinement study (0.9M, 1.8M, 3.6M DOF) with explicit percentage changes: deflection 1.2% and stress 2.1% between medium and fine meshes. Linear extrapolation yields hotspot stress 328 ± 8 MPa. Element quality metrics (Jacobian &gt; 0.55, skewness &lt; 0.75) are reported. Fine mesh adopted for reporting. Remaining discretization impact quantified and within stated bounds. Thorough evidence with quantified uncertainty band on the extrapolated stress.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2502,19 +2430,19 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Iterative convergence demonstrated via residuals and reproducibility checks</t>
+          <t>Residual convergence targets met; contact stability and energy balance verified; reproducibility demonstrated</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Force residual target 0.1% and displacement convergence 0.1% applied. 20 substeps with automatic time-stepping; contact penetration max 5.8 µm at load peak; contact status stable after substep 7. Pivot checks clean; energy balance within 0.4% at final substep. Repeat run from different initial contact status produced identical deflection within 0.2%. Penalty sensitivity study: doubling normal penalty changed hotspot stress &lt;1%; switching to pure penalty showed no global response change. Comprehensive solver health evidence.</t>
+          <t>Slide 6 documents force and displacement residual targets (0.1%), 20-substep automatic time stepping, max contact penetration 5.8 µm, energy balance within 0.4%, clean pivot checks, and stable contact status after substep 7. A reproducibility check with different initial contact status produced deflection agreement within 0.2%. Penalty sensitivity study showed &lt; 1% stress change. Thorough evidence for solver health at PDR stage.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2543,12 +2471,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent peer review of model setup with documented findings and resolution</t>
+          <t>Independent peer review of setup; boundary condition and load application verified; model register maintained</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Independent peer check by M. Alvarez: re-meshed with 0.6 mm hotspot sizing — stress within 2.4%, deflection within 0.6% of primary results. Review comments addressed (added contact sanity test, documented penalty sensitivity). All model configuration items (CAD Rev C, material lot 7A-26, Ansys 2024 R1, contact settings v2) referenced in Model Register MR-AVB-003-PDR. Boundary conditions (fixed bolt circle) confirmed to match test fixture. Workbench Named Selections and solution control XML exported for reproducibility.</t>
+          <t>Slide 12 reports independent cross-check by M. Alvarez (re-meshed at 0.6 mm hotspot sizing): stress within 2.4%, deflection within 0.6%. Comments were addressed (contact sanity test added, penalty sensitivity documented). Full traceability maintained in Model Register MR-AVB-003-PDR linking CAD Rev C, material lot, solver version, and contact settings version. Boundary conditions cross-checked against test fixture configuration (Slide 3).</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2577,12 +2505,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing physics choices justified and key limitations documented</t>
+          <t>Governing physics and simplifying assumptions documented with justification; known limitations acknowledged</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Quasi-static response with geometric nonlinearity OFF justified by max rotations &lt;3°. Frictional contact (small sliding) selected for bracket-base plate interface; bonded at PCB interface justified by &lt;2% stiffness contribution. Bilinear kinematic hardening included for overload checks; not engaged at PDR limit loads. Known omissions explicitly documented: acoustic/PSD, thermal coupling, fatigue, manufacturing tolerances — all with rationale (load-path dominance and back-of-envelope comparisons). Physics scope is appropriate and bounded; thermal knockdown not applied at PDR (identified as gap).</t>
+          <t>Slide 2 explicitly documents included physics (quasi-static, contact nonlinearity, geometric nonlinearity off) and deliberate exclusions (acoustic/PSD, thermal coupling, fatigue, manufacturing tolerances) with engineering rationale (rotations &lt; 3°, thermal effects small at PDR). SOLID186 quadratic tet selection and contact formulation (augmented Lagrange) are identified. Limitations (CDR gaps) are tracked in Slide 13. Model form is adequately justified for PDR scope; no turbulence or fluid physics involved.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2611,12 +2539,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties and loads from traceable measurements with uncertainty characterization</t>
+          <t>Material properties from testing or traceable handbooks; loads and BCs from measurements; input uncertainties characterised</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Material: MMPDS-17 allowables plus mill cert and 3 tensile coupons from sister plate (E=72.1±0.8 GPa, Fy=442±6 MPa). Elastic modulus lot scatter ±1.2 GPa documented. Bolt preload from torque equation (K=0.22) and ultrasonic measurement during test (9.1–10.0 kN range). Friction from NASA-HDBK-5080 and slip-test range 0.23–0.28. Temperature sensitivity (E drop ~1.5% over 20–60 C) assessed in sensitivity study. Geometry from CAD Rev C via STEP with fillets preserved. Input distributions formally defined for LHC sweep. Gaps: direct friction measurement for flight washer-lube stack and final torque-tension scatter with production tooling outstanding.</t>
+          <t>Slide 7 provides MMPDS-17 reference, mill certificate for Heat 7A-26, and 3-coupon tensile data (E = 72.1 ± 0.8 GPa, Fy = 442 ± 6 MPa). Bolt preload from torque equation with K=0.22; confirmed 9.1–10.0 kN by ultrasonic meter in test. Friction µ from NASA-HDBK-5080 and slip-test range 0.23–0.28. Temperature sensitivity study performed (±1.5% E drop). Input uncertainty distributions quantified for LH sweep (Slide 10). Thorough characterisation with traceable sources and quantified uncertainty.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2645,12 +2573,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article representative of flight configuration with sample count documented</t>
+          <t>Test article representative of flight configuration; sample count and geometry documented</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>One single bracket specimen tested on a 12 mm 7075 base plate with calibrated preload and adapter at avionics CG pad. Four strain gauges (G1–G4), LVDT, and DIC instrumentation used. Only one specimen tested; no statistical characterization across multiple articles. Article is described as using the same alloy and base-plate material but it is a subcomponent test, not a full flight assembly. Sample size is minimal — a single specimen provides limited statistical coverage and is a noted gap (one additional instrumented-bolt test recommended).</t>
+          <t>Slide 9 describes a single bracket mounted to a 12 mm 7075 base plate with calibrated torque wrench preload. Only one physical test article is referenced; no replicate specimens or statistical characterisation of test-article variability are reported. The article is described as production-representative in geometry but no formal statistical sampling justification is provided. Basic evidence with limited sample count.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2679,12 +2607,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Calibrated instrumentation, controlled loading, and measurement uncertainty reported</t>
+          <t>Calibrated instrumentation; controlled loading; measurement uncertainties reported</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Calibrated torque wrench and ultrasonic bolt-load meter used; bolt preload scatter 9.1–10.0 kN measured and reported. Friction coefficient measured from slip test (0.23–0.28 range). DIC used for yield-onset determination. Load applied via adapter at avionics CG pad with fixed base matching test fixture. Instrumentation calibration certificates and measurement uncertainty for strain gauges and LVDT are not explicitly cited in the report, which is a minor gap. Overall test conditions are well-characterised relative to PDR expectations.</t>
+          <t>Slide 9 documents calibrated torque wrench for preload, ultrasonic bolt meter (reading 9.1–10.0 kN scatter), four strain gauges (G1–G4), LVDT at connector face, and DIC for plasticity onset detection. Load application via adapter at avionics CG pad. Friction slip test performed to bound µ (0.23–0.28). Specific instrument calibration records and formal uncertainty budgets are not cited but multiple independent measurement channels provide cross-checks. Adequate evidence for PDR stage.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2713,12 +2641,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model inputs shown to match test conditions with uncertainty ranges compared</t>
+          <t>Model input parameters matched to test conditions with documented comparison of nominal and measured values</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Bolt preload in model (9.5 kN uniform) aligns with measured test range mean; scatter 9.1–10.0 kN documented and mapped to ±10% sensitivity. Friction µ=0.25 aligns with measured slip-test mean 0.23–0.28. Boundary conditions (fixed bolt circle) confirmed to match test fixture geometry. Preload variation across bolts is captured in sensitivity sweeps. Input parameter matching is systematic but is not fully propagated as a formal measurement-uncertainty budget through to output uncertainty — this is partially addressed by the LHC sweep.</t>
+          <t>Slide 9 directly compares model inputs to measured test conditions: bolt preload nominal 9.5 kN vs measured 9.1–10.0 kN; friction µ = 0.25 vs slip-test range 0.23–0.28; boundary conditions (fixed at bolt circle) matched to test fixture. Preload scatter is within the ±10% parametric sweep range. The base plate geometry (12 mm 7075) matches the model configuration. Adequate matching with documented rationale for remaining differences.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2747,12 +2675,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of predictions to measurements with error metrics on primary QoIs</t>
+          <t>Quantitative comparison of model predictions to experimental measurements at multiple output locations; error percentages reported</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Load-deflection stiffness: model 7.52 kN/mm vs test 7.24 kN/mm (+3.9%). Peak fillet strain G1: model 3,250 µε vs test 3,120 µε (+4.2%). Yield onset: model 27.5 kN vs test 27.0–27.5 kN (&lt;2%). Multiple comparison points (stiffness, strain, yield onset) across different response types. Errors are modest and consistent in sign (model slightly stiff). No formal statistical validation metric (e.g., u-pooled, area validation metric) or experimental uncertainty bounds reported for the test quantities, limiting the score.</t>
+          <t>Slide 9 reports three quantitative comparisons: load–deflection slope (+3.9%), peak fillet strain at G1 (+4.2%), and plasticity onset load (model 27.5 kN vs test 27.0–27.5 kN). Multiple output types (global stiffness, local strain, nonlinear onset) are compared. Errors are below 5% across all metrics. No formal statistical validation metric (e.g., MAPE, u-pooled) is computed, and only one test replicate limits statistical confidence, but quantitative agreement at multiple points is well documented for PDR stage.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2781,12 +2709,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs directly address the PDR acceptance criteria and are measurable both computationally and experimentally</t>
+          <t>Model QoIs (peak stress, connector deflection, interface contact pressure) directly address the PDR acceptance criteria and are measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Three QoIs map directly to PDR acceptance targets: (1) von Mises stress at critical fillet → yield FoS; (2) connector-face deflection → stiffness limit; (3) minimum contact pressure → joint integrity. All three were predicted by the model, all three were compared against acceptance targets (including 95th-percentile UQ outcomes), and the primary QoIs (deflection, strain) were measured in the subcomponent test. The connection between model output and decision criteria is explicit and complete.</t>
+          <t>The three primary QoIs — yield safety factor (from peak von Mises stress), connector-face deflection, and interface contact pressure — are explicitly mapped to the three PDR acceptance targets in Slides 1 and 11. All three are computed in the FEA and two (deflection, strain proxy for stress) were directly measured in the subcomponent test. The LH sweep provides 95th-percentile values for each QoI against the acceptance limits. Thorough linkage between decision need and model outputs.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2815,12 +2743,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions (geometry, loads, material, boundary conditions) representative of COU; gaps documented</t>
+          <t>Validation test geometry, loads, boundary conditions, and material match the COU; gaps to flight conditions documented</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Subcomponent test used the same alloy, same bolt class, same CG-pad loading geometry, and same base-plate fixity as the COU. Friction and preload ranges tested span the COU nominal. NAFEMS/analytical benchmarks cover the element types and contact algorithm used. Gaps clearly documented: no dynamic (PSD/modal) validation, no thermal loading, no fatigue or fretting test, no production-representative bolt torque scatter, no flight-representative washer-lube friction data. Validation is adequate for quasi-static PDR scope but incompleteness relative to full flight COU is acknowledged and tracked for CDR.</t>
+          <t>The subcomponent test used the same bracket geometry (Rev C), same base plate alloy (7075), same bolt class (12.9), same nominal preload, and same load application point as the COU. Boundary conditions (fixed bolt circle) were matched to the test fixture. Gaps are explicitly documented in Slides 2 and 13: acoustic/PSD, thermal coupling, fatigue, and manufacturing tolerance effects are out of scope for this PDR validation package and tracked as CDR deliverables. Validation is adequate for the static PDR load case but does not cover the full flight envelope; gaps are acknowledged.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -3005,7 +2933,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>All three PDR acceptance criteria are satisfied with margin: yield FoS = 1.36 nominal (1.29 at 95th percentile) ≥ 1.25 target; connector-face deflection 0.314 mm nominal (0.329 mm at 95th percentile) &lt; 0.40 mm limit; minimum contact pressure &gt;4.2 MPa indicating no interface lift-off. Model credibility is adequate for PDR scope — code benchmarks, three-level mesh convergence, peer review, material lot testing, and subcomponent test comparison (errors &lt;5%) are all in hand. Uncertainties in bolt preload, friction, modulus, and fillet geometry are quantified via Latin Hypercube sampling and remain within acceptable margins. Acceptance is conditioned on maintaining assembly work instruction requirements (µ ≥ 0.22, torque ≥ 5.5 N·m) and completing the identified CDR tasks: PSD/modal analysis and correlation, thermal coupling, fatigue assessment, direct flight washer-lube friction measurement, production torque-tension characterisation, additional instrumented-bolt subcomponent test, and hexahedral-dominant hotspot mesh spot-check.</t>
+          <t>The FEA model of LTV2-AVB-003 meets all three PDR acceptance targets: yield FoS = 1.36 nominal (1.29 at 95th percentile, exceeding the ≥ 1.25 requirement), connector-face deflection = 0.314 mm nominal (0.329 mm at 95th percentile, below 0.40 mm limit), and positive interface contact pressure maintained under all load conditions. Model credibility is supported by a three-level mesh convergence study, multiple analytical benchmarks, independent peer review by M. Alvarez, traceable material data, and a subcomponent test comparison with errors below 5% across all measured outputs. A Latin hypercube UQ sweep with 250 samples confirms margins are maintained at the 95th percentile. Acceptance is conditional on the following CDR commitments recorded in Slide 13: (1) acoustic/PSD and thermal load cases to be added; (2) fatigue and fretting analysis to follow CDR vib environment; (3) manufacturing tolerance and hole-ovality study pending supplier capability data; (4) direct friction measurements for flight washer-lube stack; (5) one additional instrumented-bolt subcomponent test to resolve preload distribution; (6) hexahedral-dominant spot-check mesh around fillets. These open items do not invalidate PDR clearance but must be resolved before CDR.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -3015,7 +2943,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>M. Chen (Structures); peer check M. Alvarez</t>
+          <t>M. Chen; peer check M. Alvarez</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
